--- a/outputs/data_dictionary_processed.xlsx
+++ b/outputs/data_dictionary_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Customer review text</t>
+          <t>Categories of products being reviewed</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>datetime64[us]</t>
+          <t>datetime64[us, UTC]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Customer rating</t>
+          <t>Date and time review was submitted</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Product category</t>
+          <t>Customer rating</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sentiment label</t>
+          <t>Customer review text</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Date and time review was submitted</t>
+          <t>Sentiment label</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>clean_review</t>
+          <t>review_lower</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>clean_review</t>
+          <t>review_lower</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -627,27 +627,71 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cleaned review after normalisation</t>
+          <t>Normalized review</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>language_update</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>language_update</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>updated review language after reclassification</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>clean_review</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>clean_review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cleaned review after normalisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>processed_tokens</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>processed_tokens</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Tokenized, lemmatized text with stop words removed</t>
         </is>

--- a/outputs/data_dictionary_processed.xlsx
+++ b/outputs/data_dictionary_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>datetime64[us, UTC]</t>
+          <t>datetime64[us]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -656,12 +656,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>clean_review</t>
+          <t>processed_texts</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>clean_review</t>
+          <t>processed_texts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -671,29 +671,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cleaned review after normalisation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>processed_tokens</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>processed_tokens</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Tokenized, lemmatized text with stop words removed</t>
+          <t>Joined tokenized, lemmatized text with stop words removed</t>
         </is>
       </c>
     </row>
